--- a/4992_Cuenca_Pachitea/_raw_reportes_xlsx/IDConfig_65060_completo.xlsx
+++ b/4992_Cuenca_Pachitea/_raw_reportes_xlsx/IDConfig_65060_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rcc931adc09fc4c81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R2c5f22496a294f80"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,366 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1322.5747</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1171.3445</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1187.0115</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1202.8072</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1245.5581</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1408.2028</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1479.0221</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1620.5150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1652.2754</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1050.6424</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    867.7771</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    842.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    850.7490</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    859.2344</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    867.7771</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    867.7771</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    872.0698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    876.3769</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    902.5196</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    906.9268</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    920.2341</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    938.1775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1120.0509</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1140.3968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/4992_Cuenca_Pachitea/_raw_reportes_xlsx/IDConfig_65060_completo.xlsx
+++ b/4992_Cuenca_Pachitea/_raw_reportes_xlsx/IDConfig_65060_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R2c5f22496a294f80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R530534c6e0a7471f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,2406 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1181.7749</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1213.4091</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1234.7846</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1333.8059</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1408.2028</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1379.3026</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1362.1341</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1339.4429</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1379.3026</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1461.1242</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1558.0668</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1645.8947</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1982.4470</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1961.2457</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1816.4401</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1570.4420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1283.7160</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1289.2244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1305.8352</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1278.2220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    956.3496</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    965.5214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    979.3865</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    988.7014</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1075.1094</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1099.9339</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1120.0509</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1140.3968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1250.9664</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1283.7160</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1333.8059</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1362.1341</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1533.4879</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1558.0668</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1545.7487</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1539.6112</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1551.9006</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1443.3550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1267.2769</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1229.4193</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1197.5276</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1229.4193</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1267.2769</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1311.4007</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1425.7146</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1485.0166</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1533.4879</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1570.4420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1473.0418</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1539.6112</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1582.8744</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1626.8385</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1982.4470</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1954.2072</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1898.4139</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1843.5359</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1614.2058</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1582.8744</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2008.0858</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2808.7253</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2930.6770</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2801.8162</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1947.1830</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1187.0115</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1202.8072</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1224.0682</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1240.1642</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1385.0540</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1289.2244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1267.2769</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1300.2839</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1443.3550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1485.0166</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1533.4879</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1570.4420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1684.3933</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1595.3641</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1582.8744</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1533.4879</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1245.5581</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1278.2220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1485.0166</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1545.7487</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1595.3641</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1658.6703</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1677.9411</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1690.8598</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1723.4067</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1749.7016</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2421.0107</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2520.4115</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2397.6404</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2270.1233</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1084.9963</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    979.3865</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    974.7505</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    979.3865</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    984.0368</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1007.5027</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1031.3262</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1192.2624</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1362.1341</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1408.2028</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1485.0166</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1620.5150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2154.3538</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2278.2392</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2482.5340</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2653.2789</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2397.6404</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1857.1696</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1245.5581</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1181.7749</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1031.3262</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    984.0368</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    929.1772</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    850.7490</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    833.9498</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    838.1281</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    850.7490</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    859.2344</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    915.7841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    920.2341</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    924.6985</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    929.1772</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    956.3496</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    970.1288</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    965.5214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1012.2388</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    970.1288</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    863.4986</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    859.2344</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    850.7490</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    842.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    829.7857</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    833.9498</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    838.1281</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    842.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    854.9846</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    867.7771</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    863.4986</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    850.7490</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    929.1772</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    956.3496</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1012.2388</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1104.9417</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1130.1952</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1171.3445</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1224.0682</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1367.8426</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1402.3942</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1390.8198</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1362.1341</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1171.3445</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1160.9714</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1150.6555</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1145.5190</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1283.7160</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1311.4007</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1328.1831</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>24/08/2026</x:t>
         </x:is>
       </x:c>
